--- a/tame_output/ON/bt/strategyON_20241010.xlsx
+++ b/tame_output/ON/bt/strategyON_20241010.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.6%</t>
+          <t>101.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>146.8%</t>
+          <t>145.2%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.7%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>423.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-674.7%</t>
+          <t>-675.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-123.1%</t>
+          <t>-124.8%</t>
         </is>
       </c>
     </row>
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-112.6%</t>
+          <t>-113.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>77.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50098,7 +50098,7 @@
         <v>45573</v>
       </c>
       <c r="B2111" t="n">
-        <v>3.816254024004753</v>
+        <v>3.816478677444489</v>
       </c>
       <c r="C2111" t="n">
         <v>4.583867337606052</v>
@@ -50114,6 +50114,29 @@
       </c>
       <c r="G2111" t="n">
         <v>5.25199728881837</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="2" t="n">
+        <v>45574</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>3.793046482686237</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>4.568546364114659</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>-5.13485870772106</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>2.514246456712488</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>1.110064774394527</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>5.234585228751375</v>
       </c>
     </row>
   </sheetData>
